--- a/artfynd/A 22396-2025 artfynd.xlsx
+++ b/artfynd/A 22396-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,231 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125317250</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 22396, Ösjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566092</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6400335</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125317242</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 22396, Ösjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566135</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6400324</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22396-2025 artfynd.xlsx
+++ b/artfynd/A 22396-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125299827</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>125317250</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>58001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>125317242</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 22396-2025 artfynd.xlsx
+++ b/artfynd/A 22396-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125299827</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,51 +785,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125317250</v>
+        <v>125317242</v>
       </c>
       <c r="B3" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566092</v>
+        <v>566135</v>
       </c>
       <c r="R3" t="n">
-        <v>6400335</v>
+        <v>6400324</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,47 +891,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125317242</v>
+        <v>125317250</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566135</v>
+        <v>566092</v>
       </c>
       <c r="R4" t="n">
-        <v>6400324</v>
+        <v>6400335</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +982,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22396-2025 artfynd.xlsx
+++ b/artfynd/A 22396-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125299827</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125317242</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22396-2025 artfynd.xlsx
+++ b/artfynd/A 22396-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125299827</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125317242</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>125317250</v>
       </c>
       <c r="B4" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22396-2025 artfynd.xlsx
+++ b/artfynd/A 22396-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>125317242</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22396-2025 artfynd.xlsx
+++ b/artfynd/A 22396-2025 artfynd.xlsx
@@ -675,46 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125299827</v>
+        <v>125317250</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566100</v>
+        <v>566092</v>
       </c>
       <c r="R2" t="n">
-        <v>6400364</v>
+        <v>6400335</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125317242</v>
+        <v>125299827</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,7 +812,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -828,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566135</v>
+        <v>566100</v>
       </c>
       <c r="R3" t="n">
-        <v>6400324</v>
+        <v>6400364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,46 +894,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125317250</v>
+        <v>125317242</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566092</v>
+        <v>566135</v>
       </c>
       <c r="R4" t="n">
-        <v>6400335</v>
+        <v>6400324</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,6 +981,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22396-2025 artfynd.xlsx
+++ b/artfynd/A 22396-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125317250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299827</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125317242</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>